--- a/files/scripts/statistical_test_scripts/rq3_result/rq3_pairwise_wilcoxon_event_bh.xlsx
+++ b/files/scripts/statistical_test_scripts/rq3_result/rq3_pairwise_wilcoxon_event_bh.xlsx
@@ -1133,7 +1133,7 @@
         <v>5.926418324622605e-05</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0002133510596864138</v>
+        <v>0.0001185283664924521</v>
       </c>
       <c r="L11" t="b">
         <v>1</v>
@@ -1193,7 +1193,7 @@
         <v>0.01171868559976863</v>
       </c>
       <c r="K12" t="n">
-        <v>0.03515605679930589</v>
+        <v>0.02109363407958353</v>
       </c>
       <c r="L12" t="b">
         <v>1</v>
@@ -1253,7 +1253,7 @@
         <v>0.0006451158437926242</v>
       </c>
       <c r="K13" t="n">
-        <v>0.002111288216048589</v>
+        <v>0.001222324756659709</v>
       </c>
       <c r="L13" t="b">
         <v>1</v>
@@ -1441,7 +1441,7 @@
         <v>0.0006451158437926242</v>
       </c>
       <c r="K16" t="n">
-        <v>0.002111288216048589</v>
+        <v>0.001222324756659709</v>
       </c>
       <c r="L16" t="b">
         <v>1</v>
@@ -1501,7 +1501,7 @@
         <v>5.926418324622605e-05</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0002133510596864138</v>
+        <v>0.0001185283664924521</v>
       </c>
       <c r="L17" t="b">
         <v>1</v>
@@ -1561,7 +1561,7 @@
         <v>0.01171868559976863</v>
       </c>
       <c r="K18" t="n">
-        <v>0.03515605679930589</v>
+        <v>0.02109363407958353</v>
       </c>
       <c r="L18" t="b">
         <v>1</v>
@@ -2261,7 +2261,7 @@
         <v>1.538348778944639e-13</v>
       </c>
       <c r="K29" t="n">
-        <v>6.153395115778556e-13</v>
+        <v>3.257679767176882e-13</v>
       </c>
       <c r="L29" t="b">
         <v>1</v>
@@ -2321,7 +2321,7 @@
         <v>1.538348778944639e-13</v>
       </c>
       <c r="K30" t="n">
-        <v>6.153395115778556e-13</v>
+        <v>3.257679767176882e-13</v>
       </c>
       <c r="L30" t="b">
         <v>1</v>
@@ -2629,7 +2629,7 @@
         <v>1.538348778944639e-13</v>
       </c>
       <c r="K35" t="n">
-        <v>6.153395115778556e-13</v>
+        <v>3.257679767176882e-13</v>
       </c>
       <c r="L35" t="b">
         <v>1</v>
@@ -2689,7 +2689,7 @@
         <v>1.538348778944639e-13</v>
       </c>
       <c r="K36" t="n">
-        <v>6.153395115778556e-13</v>
+        <v>3.257679767176882e-13</v>
       </c>
       <c r="L36" t="b">
         <v>1</v>
@@ -3361,41 +3361,37 @@
         <v>100</v>
       </c>
       <c r="G47" t="n">
-        <v>100</v>
+        <v>89.66</v>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>10.34</v>
       </c>
       <c r="I47" t="n">
         <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>1</v>
+        <v>1.476775219335459e-67</v>
       </c>
       <c r="K47" t="n">
-        <v>1</v>
+        <v>5.063229323435859e-67</v>
       </c>
       <c r="L47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M47" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>large</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>tie</t>
-        </is>
-      </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>all ties</t>
-        </is>
-      </c>
+          <t>ApproachA</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3425,41 +3421,37 @@
         <v>100</v>
       </c>
       <c r="G48" t="n">
-        <v>100</v>
+        <v>89.66</v>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>10.34</v>
       </c>
       <c r="I48" t="n">
         <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>1</v>
+        <v>1.476775219335459e-67</v>
       </c>
       <c r="K48" t="n">
-        <v>1</v>
+        <v>5.063229323435859e-67</v>
       </c>
       <c r="L48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M48" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>large</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>tie</t>
-        </is>
-      </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>all ties</t>
-        </is>
-      </c>
+          <t>ApproachA</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3489,41 +3481,37 @@
         <v>100</v>
       </c>
       <c r="G49" t="n">
-        <v>100</v>
+        <v>89.66</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>10.34</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>1</v>
+        <v>1.476775219335459e-67</v>
       </c>
       <c r="K49" t="n">
-        <v>1</v>
+        <v>5.063229323435859e-67</v>
       </c>
       <c r="L49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M49" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>large</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>tie</t>
-        </is>
-      </c>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>all ties</t>
-        </is>
-      </c>
+          <t>ApproachA</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3742,44 +3730,40 @@
         <v>400</v>
       </c>
       <c r="F53" t="n">
-        <v>100</v>
+        <v>89.66</v>
       </c>
       <c r="G53" t="n">
         <v>100</v>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>-10.34</v>
       </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>1</v>
+        <v>1.476775219335459e-67</v>
       </c>
       <c r="K53" t="n">
-        <v>1</v>
+        <v>5.063229323435859e-67</v>
       </c>
       <c r="L53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M53" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>large</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>tie</t>
-        </is>
-      </c>
-      <c r="P53" t="inlineStr">
-        <is>
-          <t>all ties</t>
-        </is>
-      </c>
+          <t>ApproachB</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3806,44 +3790,40 @@
         <v>400</v>
       </c>
       <c r="F54" t="n">
-        <v>100</v>
+        <v>89.66</v>
       </c>
       <c r="G54" t="n">
         <v>100</v>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>-10.34</v>
       </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>1</v>
+        <v>1.476775219335459e-67</v>
       </c>
       <c r="K54" t="n">
-        <v>1</v>
+        <v>5.063229323435859e-67</v>
       </c>
       <c r="L54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M54" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>large</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>tie</t>
-        </is>
-      </c>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>all ties</t>
-        </is>
-      </c>
+          <t>ApproachB</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3870,44 +3850,40 @@
         <v>400</v>
       </c>
       <c r="F55" t="n">
-        <v>100</v>
+        <v>89.66</v>
       </c>
       <c r="G55" t="n">
         <v>100</v>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>-10.34</v>
       </c>
       <c r="I55" t="n">
         <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>1</v>
+        <v>1.476775219335459e-67</v>
       </c>
       <c r="K55" t="n">
-        <v>1</v>
+        <v>5.063229323435859e-67</v>
       </c>
       <c r="L55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M55" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>large</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>tie</t>
-        </is>
-      </c>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>all ties</t>
-        </is>
-      </c>
+          <t>ApproachB</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3949,7 +3925,7 @@
         <v>2.387238385100547e-67</v>
       </c>
       <c r="K56" t="n">
-        <v>2.148514546590492e-66</v>
+        <v>6.365969026934791e-67</v>
       </c>
       <c r="L56" t="b">
         <v>1</v>
@@ -3997,41 +3973,37 @@
         <v>100</v>
       </c>
       <c r="G57" t="n">
-        <v>100</v>
+        <v>16.13</v>
       </c>
       <c r="H57" t="n">
-        <v>0</v>
+        <v>83.87</v>
       </c>
       <c r="I57" t="n">
         <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>1</v>
+        <v>2.332500941489082e-67</v>
       </c>
       <c r="K57" t="n">
-        <v>1</v>
+        <v>6.365969026934791e-67</v>
       </c>
       <c r="L57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M57" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>large</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>tie</t>
-        </is>
-      </c>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>all ties</t>
-        </is>
-      </c>
+          <t>ApproachA</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -4061,41 +4033,37 @@
         <v>100</v>
       </c>
       <c r="G58" t="n">
-        <v>100</v>
+        <v>19.25</v>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>80.75</v>
       </c>
       <c r="I58" t="n">
         <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>1</v>
+        <v>2.387238385100547e-67</v>
       </c>
       <c r="K58" t="n">
-        <v>1</v>
+        <v>6.365969026934791e-67</v>
       </c>
       <c r="L58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M58" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>large</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>tie</t>
-        </is>
-      </c>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>all ties</t>
-        </is>
-      </c>
+          <t>ApproachA</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4125,41 +4093,37 @@
         <v>100</v>
       </c>
       <c r="G59" t="n">
-        <v>100</v>
+        <v>96.565</v>
       </c>
       <c r="H59" t="n">
-        <v>0</v>
+        <v>3.435000000000002</v>
       </c>
       <c r="I59" t="n">
         <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>1</v>
+        <v>8.345820413725095e-61</v>
       </c>
       <c r="K59" t="n">
-        <v>1</v>
+        <v>2.002996899294023e-60</v>
       </c>
       <c r="L59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M59" t="n">
-        <v>0.5</v>
+        <v>0.95</v>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>large</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>tie</t>
-        </is>
-      </c>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>all ties</t>
-        </is>
-      </c>
+          <t>ApproachA</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4189,41 +4153,37 @@
         <v>100</v>
       </c>
       <c r="G60" t="n">
-        <v>100</v>
+        <v>96.565</v>
       </c>
       <c r="H60" t="n">
-        <v>0</v>
+        <v>3.435000000000002</v>
       </c>
       <c r="I60" t="n">
         <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>1</v>
+        <v>8.345820413725095e-61</v>
       </c>
       <c r="K60" t="n">
-        <v>1</v>
+        <v>2.002996899294023e-60</v>
       </c>
       <c r="L60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M60" t="n">
-        <v>0.5</v>
+        <v>0.95</v>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>large</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>tie</t>
-        </is>
-      </c>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t>all ties</t>
-        </is>
-      </c>
+          <t>ApproachA</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4253,41 +4213,37 @@
         <v>100</v>
       </c>
       <c r="G61" t="n">
-        <v>100</v>
+        <v>96.565</v>
       </c>
       <c r="H61" t="n">
-        <v>0</v>
+        <v>3.435000000000002</v>
       </c>
       <c r="I61" t="n">
         <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>1</v>
+        <v>8.345820413725095e-61</v>
       </c>
       <c r="K61" t="n">
-        <v>1</v>
+        <v>2.002996899294023e-60</v>
       </c>
       <c r="L61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M61" t="n">
-        <v>0.5</v>
+        <v>0.95</v>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>large</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>tie</t>
-        </is>
-      </c>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>all ties</t>
-        </is>
-      </c>
+          <t>ApproachA</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4317,10 +4273,10 @@
         <v>8.56</v>
       </c>
       <c r="G62" t="n">
-        <v>100</v>
+        <v>96.565</v>
       </c>
       <c r="H62" t="n">
-        <v>-91.44</v>
+        <v>-87.7</v>
       </c>
       <c r="I62" t="n">
         <v>0</v>
@@ -4329,7 +4285,7 @@
         <v>2.387238385100547e-67</v>
       </c>
       <c r="K62" t="n">
-        <v>2.148514546590492e-66</v>
+        <v>6.365969026934791e-67</v>
       </c>
       <c r="L62" t="b">
         <v>1</v>
@@ -4374,44 +4330,40 @@
         <v>400</v>
       </c>
       <c r="F63" t="n">
-        <v>100</v>
+        <v>16.13</v>
       </c>
       <c r="G63" t="n">
-        <v>100</v>
+        <v>96.565</v>
       </c>
       <c r="H63" t="n">
-        <v>0</v>
+        <v>-79.69</v>
       </c>
       <c r="I63" t="n">
         <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>1</v>
+        <v>2.387238385100547e-67</v>
       </c>
       <c r="K63" t="n">
-        <v>1</v>
+        <v>6.365969026934791e-67</v>
       </c>
       <c r="L63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M63" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>large</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>tie</t>
-        </is>
-      </c>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>all ties</t>
-        </is>
-      </c>
+          <t>ApproachB</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4438,44 +4390,40 @@
         <v>400</v>
       </c>
       <c r="F64" t="n">
-        <v>100</v>
+        <v>19.25</v>
       </c>
       <c r="G64" t="n">
-        <v>100</v>
+        <v>96.565</v>
       </c>
       <c r="H64" t="n">
-        <v>0</v>
+        <v>-76.03999999999999</v>
       </c>
       <c r="I64" t="n">
         <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>1</v>
+        <v>2.387238385100547e-67</v>
       </c>
       <c r="K64" t="n">
-        <v>1</v>
+        <v>6.365969026934791e-67</v>
       </c>
       <c r="L64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M64" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>large</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>tie</t>
-        </is>
-      </c>
-      <c r="P64" t="inlineStr">
-        <is>
-          <t>all ties</t>
-        </is>
-      </c>
+          <t>ApproachB</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4514,16 +4462,16 @@
         <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>2.603243595271822e-59</v>
+        <v>4.033339917615288e-71</v>
       </c>
       <c r="K65" t="n">
-        <v>1.33881099185408e-58</v>
+        <v>1.936003160455338e-70</v>
       </c>
       <c r="L65" t="b">
         <v>1</v>
       </c>
       <c r="M65" t="n">
-        <v>0.9086538461538461</v>
+        <v>1</v>
       </c>
       <c r="N65" t="inlineStr">
         <is>
@@ -4574,16 +4522,16 @@
         <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>2.603243595271822e-59</v>
+        <v>4.033339917615288e-71</v>
       </c>
       <c r="K66" t="n">
-        <v>1.33881099185408e-58</v>
+        <v>1.936003160455338e-70</v>
       </c>
       <c r="L66" t="b">
         <v>1</v>
       </c>
       <c r="M66" t="n">
-        <v>0.9086538461538461</v>
+        <v>1</v>
       </c>
       <c r="N66" t="inlineStr">
         <is>
@@ -4634,16 +4582,16 @@
         <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>2.603243595271822e-59</v>
+        <v>4.033339917615288e-71</v>
       </c>
       <c r="K67" t="n">
-        <v>1.33881099185408e-58</v>
+        <v>1.936003160455338e-70</v>
       </c>
       <c r="L67" t="b">
         <v>1</v>
       </c>
       <c r="M67" t="n">
-        <v>0.9086538461538461</v>
+        <v>1</v>
       </c>
       <c r="N67" t="inlineStr">
         <is>
@@ -4685,41 +4633,37 @@
         <v>100</v>
       </c>
       <c r="G68" t="n">
-        <v>100</v>
+        <v>96.67</v>
       </c>
       <c r="H68" t="n">
-        <v>0</v>
+        <v>3.329999999999998</v>
       </c>
       <c r="I68" t="n">
         <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>1</v>
+        <v>3.878578144017659e-72</v>
       </c>
       <c r="K68" t="n">
-        <v>1</v>
+        <v>3.102862515214127e-71</v>
       </c>
       <c r="L68" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M68" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>large</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>tie</t>
-        </is>
-      </c>
-      <c r="P68" t="inlineStr">
-        <is>
-          <t>all ties</t>
-        </is>
-      </c>
+          <t>ApproachA</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4749,41 +4693,37 @@
         <v>100</v>
       </c>
       <c r="G69" t="n">
-        <v>100</v>
+        <v>96.67</v>
       </c>
       <c r="H69" t="n">
-        <v>0</v>
+        <v>3.329999999999998</v>
       </c>
       <c r="I69" t="n">
         <v>0</v>
       </c>
       <c r="J69" t="n">
-        <v>1</v>
+        <v>3.878578144017659e-72</v>
       </c>
       <c r="K69" t="n">
-        <v>1</v>
+        <v>3.102862515214127e-71</v>
       </c>
       <c r="L69" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M69" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>large</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>tie</t>
-        </is>
-      </c>
-      <c r="P69" t="inlineStr">
-        <is>
-          <t>all ties</t>
-        </is>
-      </c>
+          <t>ApproachA</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4813,41 +4753,37 @@
         <v>100</v>
       </c>
       <c r="G70" t="n">
-        <v>100</v>
+        <v>96.67</v>
       </c>
       <c r="H70" t="n">
-        <v>0</v>
+        <v>3.329999999999998</v>
       </c>
       <c r="I70" t="n">
         <v>0</v>
       </c>
       <c r="J70" t="n">
-        <v>1</v>
+        <v>3.878578144017659e-72</v>
       </c>
       <c r="K70" t="n">
-        <v>1</v>
+        <v>3.102862515214127e-71</v>
       </c>
       <c r="L70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M70" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>large</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>tie</t>
-        </is>
-      </c>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>all ties</t>
-        </is>
-      </c>
+          <t>ApproachA</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4877,25 +4813,25 @@
         <v>33.33</v>
       </c>
       <c r="G71" t="n">
-        <v>100</v>
+        <v>96.67</v>
       </c>
       <c r="H71" t="n">
-        <v>-66.67</v>
+        <v>-63.34</v>
       </c>
       <c r="I71" t="n">
         <v>0</v>
       </c>
       <c r="J71" t="n">
-        <v>2.603243595271822e-59</v>
+        <v>4.033339917615288e-71</v>
       </c>
       <c r="K71" t="n">
-        <v>1.33881099185408e-58</v>
+        <v>1.936003160455338e-70</v>
       </c>
       <c r="L71" t="b">
         <v>1</v>
       </c>
       <c r="M71" t="n">
-        <v>0.09134615384615384</v>
+        <v>0</v>
       </c>
       <c r="N71" t="inlineStr">
         <is>
@@ -4937,25 +4873,25 @@
         <v>35</v>
       </c>
       <c r="G72" t="n">
-        <v>100</v>
+        <v>96.67</v>
       </c>
       <c r="H72" t="n">
-        <v>-65</v>
+        <v>-61.67</v>
       </c>
       <c r="I72" t="n">
         <v>0</v>
       </c>
       <c r="J72" t="n">
-        <v>2.603243595271822e-59</v>
+        <v>4.033339917615288e-71</v>
       </c>
       <c r="K72" t="n">
-        <v>1.33881099185408e-58</v>
+        <v>1.936003160455338e-70</v>
       </c>
       <c r="L72" t="b">
         <v>1</v>
       </c>
       <c r="M72" t="n">
-        <v>0.09134615384615384</v>
+        <v>0</v>
       </c>
       <c r="N72" t="inlineStr">
         <is>
@@ -4997,25 +4933,25 @@
         <v>36.67</v>
       </c>
       <c r="G73" t="n">
-        <v>100</v>
+        <v>96.67</v>
       </c>
       <c r="H73" t="n">
-        <v>-63.33</v>
+        <v>-60</v>
       </c>
       <c r="I73" t="n">
         <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>2.603243595271822e-59</v>
+        <v>4.033339917615288e-71</v>
       </c>
       <c r="K73" t="n">
-        <v>1.33881099185408e-58</v>
+        <v>1.936003160455338e-70</v>
       </c>
       <c r="L73" t="b">
         <v>1</v>
       </c>
       <c r="M73" t="n">
-        <v>0.09134615384615384</v>
+        <v>0</v>
       </c>
       <c r="N73" t="inlineStr">
         <is>
@@ -5171,7 +5107,7 @@
         <v>47.725</v>
       </c>
       <c r="G2" t="n">
-        <v>27.78</v>
+        <v>26.935</v>
       </c>
       <c r="H2" t="n">
         <v>20.445</v>
@@ -5183,7 +5119,7 @@
         <v>0.00048828125</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0006061422413793104</v>
+        <v>0.0006392045454545455</v>
       </c>
       <c r="L2" t="b">
         <v>1</v>
@@ -5240,16 +5176,16 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001953125</v>
+        <v>0.0009765625</v>
       </c>
       <c r="K3" t="n">
-        <v>0.00234375</v>
+        <v>0.001233552631578947</v>
       </c>
       <c r="L3" t="b">
         <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8819444444444444</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -5297,19 +5233,19 @@
         <v>8.329999999999998</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>0.03125</v>
       </c>
       <c r="K4" t="n">
-        <v>0.03571428571428571</v>
+        <v>0.03629032258064516</v>
       </c>
       <c r="L4" t="b">
         <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7013888888888888</v>
+        <v>0.6875</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -5363,7 +5299,7 @@
         <v>0.125</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1363636363636364</v>
+        <v>0.1384615384615385</v>
       </c>
       <c r="L5" t="b">
         <v>0</v>
@@ -5423,7 +5359,7 @@
         <v>0.125</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1363636363636364</v>
+        <v>0.1384615384615385</v>
       </c>
       <c r="L6" t="b">
         <v>0</v>
@@ -5483,7 +5419,7 @@
         <v>0.125</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1363636363636364</v>
+        <v>0.1384615384615385</v>
       </c>
       <c r="L7" t="b">
         <v>0</v>
@@ -5528,13 +5464,13 @@
         <v>12</v>
       </c>
       <c r="F8" t="n">
-        <v>27.78</v>
+        <v>26.935</v>
       </c>
       <c r="G8" t="n">
         <v>57.14</v>
       </c>
       <c r="H8" t="n">
-        <v>-28.105</v>
+        <v>-30.64</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -5543,7 +5479,7 @@
         <v>0.00048828125</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0006061422413793104</v>
+        <v>0.0006392045454545455</v>
       </c>
       <c r="L8" t="b">
         <v>1</v>
@@ -5594,7 +5530,7 @@
         <v>57.14</v>
       </c>
       <c r="H9" t="n">
-        <v>-25.435</v>
+        <v>-21.965</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -5603,13 +5539,13 @@
         <v>0.0009765625</v>
       </c>
       <c r="K9" t="n">
-        <v>0.001191737288135593</v>
+        <v>0.001233552631578947</v>
       </c>
       <c r="L9" t="b">
         <v>1</v>
       </c>
       <c r="M9" t="n">
-        <v>0.06944444444444445</v>
+        <v>0.04513888888888889</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -5654,22 +5590,22 @@
         <v>57.14</v>
       </c>
       <c r="H10" t="n">
-        <v>-15.745</v>
+        <v>-12.175</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0.015625</v>
+        <v>0.03125</v>
       </c>
       <c r="K10" t="n">
-        <v>0.01844262295081967</v>
+        <v>0.03629032258064516</v>
       </c>
       <c r="L10" t="b">
         <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.2361111111111111</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -5723,7 +5659,7 @@
         <v>2.384185791015625e-07</v>
       </c>
       <c r="K11" t="n">
-        <v>3.301180326021635e-07</v>
+        <v>3.576278686523438e-07</v>
       </c>
       <c r="L11" t="b">
         <v>1</v>
@@ -5783,7 +5719,7 @@
         <v>0.4100396633148193</v>
       </c>
       <c r="K12" t="n">
-        <v>0.4406396381890595</v>
+        <v>0.4473159963434392</v>
       </c>
       <c r="L12" t="b">
         <v>0</v>
@@ -5831,25 +5767,25 @@
         <v>13.57</v>
       </c>
       <c r="G13" t="n">
-        <v>13.64</v>
+        <v>13.33</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.5800000000000001</v>
+        <v>-0.5600000000000005</v>
       </c>
       <c r="I13" t="n">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="J13" t="n">
-        <v>0.8932116031646729</v>
+        <v>0.7313888072967529</v>
       </c>
       <c r="K13" t="n">
-        <v>0.9131756056149267</v>
+        <v>0.7631883206574813</v>
       </c>
       <c r="L13" t="b">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>0.4914933837429111</v>
+        <v>0.5066162570888468</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -5858,7 +5794,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>ApproachA</t>
+          <t>ApproachB</t>
         </is>
       </c>
       <c r="P13" t="inlineStr"/>
@@ -5903,7 +5839,7 @@
         <v>2.384185791015625e-07</v>
       </c>
       <c r="K14" t="n">
-        <v>3.301180326021635e-07</v>
+        <v>3.576278686523438e-07</v>
       </c>
       <c r="L14" t="b">
         <v>1</v>
@@ -5963,7 +5899,7 @@
         <v>1.192092895507812e-06</v>
       </c>
       <c r="K15" t="n">
-        <v>1.589457194010416e-06</v>
+        <v>1.682954676011029e-06</v>
       </c>
       <c r="L15" t="b">
         <v>1</v>
@@ -6023,7 +5959,7 @@
         <v>0.8229274749755859</v>
       </c>
       <c r="K16" t="n">
-        <v>0.8678228158937921</v>
+        <v>0.8433771027700233</v>
       </c>
       <c r="L16" t="b">
         <v>0</v>
@@ -6083,7 +6019,7 @@
         <v>2.384185791015625e-07</v>
       </c>
       <c r="K17" t="n">
-        <v>3.301180326021635e-07</v>
+        <v>3.576278686523438e-07</v>
       </c>
       <c r="L17" t="b">
         <v>1</v>
@@ -6143,7 +6079,7 @@
         <v>2.384185791015625e-07</v>
       </c>
       <c r="K18" t="n">
-        <v>3.301180326021635e-07</v>
+        <v>3.576278686523438e-07</v>
       </c>
       <c r="L18" t="b">
         <v>1</v>
@@ -6188,7 +6124,7 @@
         <v>23</v>
       </c>
       <c r="F19" t="n">
-        <v>13.64</v>
+        <v>13.33</v>
       </c>
       <c r="G19" t="n">
         <v>13.64</v>
@@ -6197,23 +6133,23 @@
         <v>-0.9499999999999993</v>
       </c>
       <c r="I19" t="n">
-        <v>124.5</v>
+        <v>122</v>
       </c>
       <c r="J19" t="n">
-        <v>0.9482252929562537</v>
+        <v>0.8838460571465129</v>
       </c>
       <c r="K19" t="n">
-        <v>0.9482252929562536</v>
+        <v>0.8838460571465129</v>
       </c>
       <c r="L19" t="b">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.44234404536862</v>
+        <v>0.4196597353497165</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>small</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -6254,22 +6190,22 @@
         <v>12.24</v>
       </c>
       <c r="H20" t="n">
-        <v>5.52</v>
+        <v>5.550000000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="J20" t="n">
-        <v>4.471124253338281e-08</v>
+        <v>2.487789406985899e-07</v>
       </c>
       <c r="K20" t="n">
-        <v>6.849381834901196e-08</v>
+        <v>3.655527291897647e-07</v>
       </c>
       <c r="L20" t="b">
         <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>0.9438775510204082</v>
+        <v>0.9563492063492064</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -6311,25 +6247,25 @@
         <v>7.35</v>
       </c>
       <c r="G21" t="n">
-        <v>4.58</v>
+        <v>4.455</v>
       </c>
       <c r="H21" t="n">
-        <v>2.02</v>
+        <v>2.319999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>89</v>
+        <v>78.5</v>
       </c>
       <c r="J21" t="n">
-        <v>5.804848178000667e-06</v>
+        <v>3.090184895751452e-06</v>
       </c>
       <c r="K21" t="n">
-        <v>7.463376228858001e-06</v>
+        <v>4.197987028190652e-06</v>
       </c>
       <c r="L21" t="b">
         <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>0.7590702947845805</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -6371,25 +6307,25 @@
         <v>5.73</v>
       </c>
       <c r="G22" t="n">
-        <v>3.56</v>
+        <v>3.7</v>
       </c>
       <c r="H22" t="n">
         <v>2.085</v>
       </c>
       <c r="I22" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J22" t="n">
-        <v>1.325261405577772e-06</v>
+        <v>1.41254233028078e-06</v>
       </c>
       <c r="K22" t="n">
-        <v>1.734887658210901e-06</v>
+        <v>1.955827841927234e-06</v>
       </c>
       <c r="L22" t="b">
         <v>1</v>
       </c>
       <c r="M22" t="n">
-        <v>0.7301587301587301</v>
+        <v>0.7278911564625851</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -6443,7 +6379,7 @@
         <v>1.646879902703648e-08</v>
       </c>
       <c r="K23" t="n">
-        <v>2.578551807615624e-08</v>
+        <v>2.757566348713085e-08</v>
       </c>
       <c r="L23" t="b">
         <v>1</v>
@@ -6503,7 +6439,7 @@
         <v>1.187528716428739e-07</v>
       </c>
       <c r="K24" t="n">
-        <v>1.781293074643109e-07</v>
+        <v>1.943228808701573e-07</v>
       </c>
       <c r="L24" t="b">
         <v>1</v>
@@ -6563,7 +6499,7 @@
         <v>0.8316635318982174</v>
       </c>
       <c r="K25" t="n">
-        <v>0.8678228158937921</v>
+        <v>0.8433771027700233</v>
       </c>
       <c r="L25" t="b">
         <v>0</v>
@@ -6614,16 +6550,16 @@
         <v>5.585</v>
       </c>
       <c r="H26" t="n">
-        <v>7.5975</v>
+        <v>7.265000000000001</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>1.647408099309982e-08</v>
+        <v>4.547473508864641e-13</v>
       </c>
       <c r="K26" t="n">
-        <v>2.578551807615624e-08</v>
+        <v>8.185452315956354e-13</v>
       </c>
       <c r="L26" t="b">
         <v>1</v>
@@ -6668,28 +6604,28 @@
         <v>42</v>
       </c>
       <c r="F27" t="n">
-        <v>4.58</v>
+        <v>4.455</v>
       </c>
       <c r="G27" t="n">
         <v>5.585</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.2324999999999993</v>
+        <v>-0.1925000000000001</v>
       </c>
       <c r="I27" t="n">
-        <v>441.5</v>
+        <v>422</v>
       </c>
       <c r="J27" t="n">
-        <v>0.9004926110924971</v>
+        <v>0.7122227637754117</v>
       </c>
       <c r="K27" t="n">
-        <v>0.9131756056149267</v>
+        <v>0.754118220468083</v>
       </c>
       <c r="L27" t="b">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.4744897959183674</v>
+        <v>0.4682539682539683</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -6728,7 +6664,7 @@
         <v>42</v>
       </c>
       <c r="F28" t="n">
-        <v>3.56</v>
+        <v>3.7</v>
       </c>
       <c r="G28" t="n">
         <v>5.585</v>
@@ -6737,19 +6673,19 @@
         <v>-1.6</v>
       </c>
       <c r="I28" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="J28" t="n">
-        <v>9.818973152847362e-07</v>
+        <v>8.643826460024959e-07</v>
       </c>
       <c r="K28" t="n">
-        <v>1.333898239632095e-06</v>
+        <v>1.244711010243594e-06</v>
       </c>
       <c r="L28" t="b">
         <v>1</v>
       </c>
       <c r="M28" t="n">
-        <v>0.2607709750566893</v>
+        <v>0.2653061224489796</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -6791,25 +6727,25 @@
         <v>37.905</v>
       </c>
       <c r="G29" t="n">
-        <v>31.48</v>
+        <v>31.465</v>
       </c>
       <c r="H29" t="n">
         <v>7.310000000000002</v>
       </c>
       <c r="I29" t="n">
-        <v>27700.5</v>
+        <v>26904.5</v>
       </c>
       <c r="J29" t="n">
-        <v>8.709978202486797e-27</v>
+        <v>5.809087336959167e-28</v>
       </c>
       <c r="K29" t="n">
-        <v>1.607995975843716e-26</v>
+        <v>1.100669179634368e-27</v>
       </c>
       <c r="L29" t="b">
         <v>1</v>
       </c>
       <c r="M29" t="n">
-        <v>0.759532104320898</v>
+        <v>0.7640501766100547</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
@@ -6851,25 +6787,25 @@
         <v>41.85</v>
       </c>
       <c r="G30" t="n">
-        <v>34.33</v>
+        <v>34.48</v>
       </c>
       <c r="H30" t="n">
         <v>10</v>
       </c>
       <c r="I30" t="n">
-        <v>24793</v>
+        <v>24983</v>
       </c>
       <c r="J30" t="n">
-        <v>3.286373001545587e-31</v>
+        <v>6.55506525850639e-31</v>
       </c>
       <c r="K30" t="n">
-        <v>6.760538746036636e-31</v>
+        <v>1.311013051701278e-30</v>
       </c>
       <c r="L30" t="b">
         <v>1</v>
       </c>
       <c r="M30" t="n">
-        <v>0.7410001451589491</v>
+        <v>0.7407763584458316</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -6911,25 +6847,25 @@
         <v>51.21</v>
       </c>
       <c r="G31" t="n">
-        <v>38.04</v>
+        <v>38.02</v>
       </c>
       <c r="H31" t="n">
-        <v>13.1</v>
+        <v>13.11</v>
       </c>
       <c r="I31" t="n">
-        <v>10741.5</v>
+        <v>10652.5</v>
       </c>
       <c r="J31" t="n">
-        <v>1.532316504167253e-56</v>
+        <v>6.098914174881242e-57</v>
       </c>
       <c r="K31" t="n">
-        <v>4.086177344446008e-56</v>
+        <v>1.416522001907901e-56</v>
       </c>
       <c r="L31" t="b">
         <v>1</v>
       </c>
       <c r="M31" t="n">
-        <v>0.8061765132820439</v>
+        <v>0.8070172255286205</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
@@ -6983,7 +6919,7 @@
         <v>1.221253279971577e-65</v>
       </c>
       <c r="K32" t="n">
-        <v>4.885013119886308e-65</v>
+        <v>3.140365577069769e-65</v>
       </c>
       <c r="L32" t="b">
         <v>1</v>
@@ -7043,7 +6979,7 @@
         <v>5.361582643592803e-10</v>
       </c>
       <c r="K33" t="n">
-        <v>8.773498871333678e-10</v>
+        <v>9.191284531873378e-10</v>
       </c>
       <c r="L33" t="b">
         <v>1</v>
@@ -7103,7 +7039,7 @@
         <v>4.201378447301267e-28</v>
       </c>
       <c r="K34" t="n">
-        <v>7.960506531728717e-28</v>
+        <v>8.175655356910575e-28</v>
       </c>
       <c r="L34" t="b">
         <v>1</v>
@@ -7148,28 +7084,28 @@
         <v>498</v>
       </c>
       <c r="F35" t="n">
-        <v>31.48</v>
+        <v>31.465</v>
       </c>
       <c r="G35" t="n">
         <v>43.92</v>
       </c>
       <c r="H35" t="n">
-        <v>-13.385</v>
+        <v>-13.58</v>
       </c>
       <c r="I35" t="n">
-        <v>4546</v>
+        <v>4161.5</v>
       </c>
       <c r="J35" t="n">
-        <v>8.089763848075026e-72</v>
+        <v>9.344317594485901e-73</v>
       </c>
       <c r="K35" t="n">
-        <v>6.471811078460022e-71</v>
+        <v>7.475454075588721e-72</v>
       </c>
       <c r="L35" t="b">
         <v>1</v>
       </c>
       <c r="M35" t="n">
-        <v>0.1041535620393219</v>
+        <v>0.1015588458250673</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
@@ -7208,28 +7144,28 @@
         <v>498</v>
       </c>
       <c r="F36" t="n">
-        <v>34.33</v>
+        <v>34.48</v>
       </c>
       <c r="G36" t="n">
         <v>43.92</v>
       </c>
       <c r="H36" t="n">
-        <v>-11.64</v>
+        <v>-11.51</v>
       </c>
       <c r="I36" t="n">
-        <v>7243.5</v>
+        <v>7453.5</v>
       </c>
       <c r="J36" t="n">
-        <v>2.041387191104076e-65</v>
+        <v>6.244837326614357e-65</v>
       </c>
       <c r="K36" t="n">
-        <v>7.73578303997334e-65</v>
+        <v>1.550442370745634e-64</v>
       </c>
       <c r="L36" t="b">
         <v>1</v>
       </c>
       <c r="M36" t="n">
-        <v>0.1772027870518217</v>
+        <v>0.177489072756891</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
@@ -7268,28 +7204,28 @@
         <v>498</v>
       </c>
       <c r="F37" t="n">
-        <v>38.04</v>
+        <v>38.02</v>
       </c>
       <c r="G37" t="n">
         <v>43.92</v>
       </c>
       <c r="H37" t="n">
-        <v>-7.669999999999998</v>
+        <v>-7.922499999999999</v>
       </c>
       <c r="I37" t="n">
-        <v>6934</v>
+        <v>6719</v>
       </c>
       <c r="J37" t="n">
-        <v>4.091547268298832e-54</v>
+        <v>7.260753727435013e-55</v>
       </c>
       <c r="K37" t="n">
-        <v>9.819713443917198e-54</v>
+        <v>1.633669588672878e-54</v>
       </c>
       <c r="L37" t="b">
         <v>1</v>
       </c>
       <c r="M37" t="n">
-        <v>0.2859187755036209</v>
+        <v>0.2833905904743472</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
@@ -7328,28 +7264,28 @@
         <v>2664</v>
       </c>
       <c r="F38" t="n">
-        <v>23.68</v>
+        <v>23.695</v>
       </c>
       <c r="G38" t="n">
-        <v>27.54</v>
+        <v>27.52</v>
       </c>
       <c r="H38" t="n">
-        <v>-4.040000000000003</v>
+        <v>-3.995000000000001</v>
       </c>
       <c r="I38" t="n">
-        <v>324953.5</v>
+        <v>320848.5</v>
       </c>
       <c r="J38" t="n">
-        <v>1.44440270717659e-291</v>
+        <v>2.040466348060846e-293</v>
       </c>
       <c r="K38" t="n">
-        <v>1.485671355953064e-290</v>
+        <v>2.09876538657687e-292</v>
       </c>
       <c r="L38" t="b">
         <v>1</v>
       </c>
       <c r="M38" t="n">
-        <v>0.2051196748550352</v>
+        <v>0.2047766375609844</v>
       </c>
       <c r="N38" t="inlineStr">
         <is>
@@ -7388,16 +7324,16 @@
         <v>2664</v>
       </c>
       <c r="F39" t="n">
-        <v>13.235</v>
+        <v>13.205</v>
       </c>
       <c r="G39" t="n">
-        <v>18.475</v>
+        <v>18.415</v>
       </c>
       <c r="H39" t="n">
-        <v>-5.42</v>
+        <v>-5.469999999999999</v>
       </c>
       <c r="I39" t="n">
-        <v>41344.5</v>
+        <v>46171</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -7409,7 +7345,7 @@
         <v>1</v>
       </c>
       <c r="M39" t="n">
-        <v>0.1192856003526049</v>
+        <v>0.1193077227001777</v>
       </c>
       <c r="N39" t="inlineStr">
         <is>
@@ -7448,16 +7384,16 @@
         <v>2664</v>
       </c>
       <c r="F40" t="n">
-        <v>8.949999999999999</v>
+        <v>8.94</v>
       </c>
       <c r="G40" t="n">
-        <v>13.87</v>
+        <v>13.89</v>
       </c>
       <c r="H40" t="n">
         <v>-5.04</v>
       </c>
       <c r="I40" t="n">
-        <v>36004.5</v>
+        <v>36448</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -7469,7 +7405,7 @@
         <v>1</v>
       </c>
       <c r="M40" t="n">
-        <v>0.1015446753059366</v>
+        <v>0.1013201405234063</v>
       </c>
       <c r="N40" t="inlineStr">
         <is>
@@ -7508,16 +7444,16 @@
         <v>2664</v>
       </c>
       <c r="F41" t="n">
-        <v>23.68</v>
+        <v>23.695</v>
       </c>
       <c r="G41" t="n">
         <v>15.18</v>
       </c>
       <c r="H41" t="n">
-        <v>8.065000000000001</v>
+        <v>8.119999999999997</v>
       </c>
       <c r="I41" t="n">
-        <v>3779.5</v>
+        <v>3793.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -7529,7 +7465,7 @@
         <v>1</v>
       </c>
       <c r="M41" t="n">
-        <v>0.9734703030733436</v>
+        <v>0.9742189402240078</v>
       </c>
       <c r="N41" t="inlineStr">
         <is>
@@ -7568,28 +7504,28 @@
         <v>2664</v>
       </c>
       <c r="F42" t="n">
-        <v>13.235</v>
+        <v>13.205</v>
       </c>
       <c r="G42" t="n">
         <v>15.18</v>
       </c>
       <c r="H42" t="n">
-        <v>-2.167499999999999</v>
+        <v>-2.2075</v>
       </c>
       <c r="I42" t="n">
-        <v>562118.5</v>
+        <v>561952</v>
       </c>
       <c r="J42" t="n">
-        <v>1.769125809693663e-204</v>
+        <v>9.436502711524469e-205</v>
       </c>
       <c r="K42" t="n">
-        <v>1.592213228724297e-203</v>
+        <v>8.492852440372022e-204</v>
       </c>
       <c r="L42" t="b">
         <v>1</v>
       </c>
       <c r="M42" t="n">
-        <v>0.2816849084444805</v>
+        <v>0.2794259631252874</v>
       </c>
       <c r="N42" t="inlineStr">
         <is>
@@ -7628,16 +7564,16 @@
         <v>2664</v>
       </c>
       <c r="F43" t="n">
-        <v>8.949999999999999</v>
+        <v>8.94</v>
       </c>
       <c r="G43" t="n">
         <v>15.18</v>
       </c>
       <c r="H43" t="n">
-        <v>-6.1475</v>
+        <v>-6.162500000000001</v>
       </c>
       <c r="I43" t="n">
-        <v>61872.5</v>
+        <v>61823</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -7649,7 +7585,7 @@
         <v>1</v>
       </c>
       <c r="M43" t="n">
-        <v>0.07464798695091487</v>
+        <v>0.07469991105970836</v>
       </c>
       <c r="N43" t="inlineStr">
         <is>
@@ -7688,16 +7624,16 @@
         <v>2664</v>
       </c>
       <c r="F44" t="n">
-        <v>27.54</v>
+        <v>27.52</v>
       </c>
       <c r="G44" t="n">
         <v>15.18</v>
       </c>
       <c r="H44" t="n">
-        <v>12.18</v>
+        <v>12.21</v>
       </c>
       <c r="I44" t="n">
-        <v>5246</v>
+        <v>5978</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -7709,7 +7645,7 @@
         <v>1</v>
       </c>
       <c r="M44" t="n">
-        <v>0.9889362194401609</v>
+        <v>0.9888106011416822</v>
       </c>
       <c r="N44" t="inlineStr">
         <is>
@@ -7748,16 +7684,16 @@
         <v>2664</v>
       </c>
       <c r="F45" t="n">
-        <v>18.475</v>
+        <v>18.415</v>
       </c>
       <c r="G45" t="n">
         <v>15.18</v>
       </c>
       <c r="H45" t="n">
-        <v>2.999999999999997</v>
+        <v>2.972499999999998</v>
       </c>
       <c r="I45" t="n">
-        <v>214269</v>
+        <v>221480</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -7769,7 +7705,7 @@
         <v>1</v>
       </c>
       <c r="M45" t="n">
-        <v>0.7468862443524605</v>
+        <v>0.7454499826402979</v>
       </c>
       <c r="N45" t="inlineStr">
         <is>
@@ -7808,7 +7744,7 @@
         <v>2664</v>
       </c>
       <c r="F46" t="n">
-        <v>13.87</v>
+        <v>13.89</v>
       </c>
       <c r="G46" t="n">
         <v>15.18</v>
@@ -7817,19 +7753,19 @@
         <v>-1.015</v>
       </c>
       <c r="I46" t="n">
-        <v>1156183.5</v>
+        <v>1162986</v>
       </c>
       <c r="J46" t="n">
-        <v>9.495243422859468e-55</v>
+        <v>1.365829814466042e-53</v>
       </c>
       <c r="K46" t="n">
-        <v>2.441634023021006e-54</v>
+        <v>2.979992322471364e-53</v>
       </c>
       <c r="L46" t="b">
         <v>1</v>
       </c>
       <c r="M46" t="n">
-        <v>0.3932728477351225</v>
+        <v>0.3936790816717619</v>
       </c>
       <c r="N46" t="inlineStr">
         <is>
@@ -7868,32 +7804,32 @@
         <v>400</v>
       </c>
       <c r="F47" t="n">
-        <v>9.18</v>
+        <v>9.43</v>
       </c>
       <c r="G47" t="n">
-        <v>3.92</v>
+        <v>7.765000000000001</v>
       </c>
       <c r="H47" t="n">
-        <v>3.495</v>
+        <v>0.8499999999999996</v>
       </c>
       <c r="I47" t="n">
-        <v>13187.5</v>
+        <v>34231</v>
       </c>
       <c r="J47" t="n">
-        <v>4.692968315310286e-31</v>
+        <v>0.01119012136909999</v>
       </c>
       <c r="K47" t="n">
-        <v>9.385936630620572e-31</v>
+        <v>0.01365574133178304</v>
       </c>
       <c r="L47" t="b">
         <v>1</v>
       </c>
       <c r="M47" t="n">
-        <v>0.750921875</v>
+        <v>0.52550625</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>large</t>
+          <t>negligible</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -7928,37 +7864,37 @@
         <v>400</v>
       </c>
       <c r="F48" t="n">
-        <v>6.84</v>
+        <v>6.94</v>
       </c>
       <c r="G48" t="n">
-        <v>3.55</v>
+        <v>5.779999999999999</v>
       </c>
       <c r="H48" t="n">
-        <v>2.160000000000001</v>
+        <v>0.07000000000000028</v>
       </c>
       <c r="I48" t="n">
-        <v>15421.5</v>
+        <v>32677.5</v>
       </c>
       <c r="J48" t="n">
-        <v>3.985380047889337e-26</v>
+        <v>0.002225582370063115</v>
       </c>
       <c r="K48" t="n">
-        <v>7.173684086200807e-26</v>
+        <v>0.002762791907664556</v>
       </c>
       <c r="L48" t="b">
         <v>1</v>
       </c>
       <c r="M48" t="n">
-        <v>0.688846875</v>
+        <v>0.473159375</v>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>negligible</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>ApproachB</t>
+          <t>ApproachA</t>
         </is>
       </c>
       <c r="P48" t="inlineStr"/>
@@ -7988,32 +7924,32 @@
         <v>400</v>
       </c>
       <c r="F49" t="n">
-        <v>6.84</v>
+        <v>6.94</v>
       </c>
       <c r="G49" t="n">
-        <v>2.71</v>
+        <v>4.225</v>
       </c>
       <c r="H49" t="n">
-        <v>2.54</v>
+        <v>0.7650000000000001</v>
       </c>
       <c r="I49" t="n">
-        <v>8465</v>
+        <v>37650</v>
       </c>
       <c r="J49" t="n">
-        <v>1.028016353348811e-41</v>
+        <v>0.4682672276534862</v>
       </c>
       <c r="K49" t="n">
-        <v>2.313036795034825e-41</v>
+        <v>0.503212543150015</v>
       </c>
       <c r="L49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>0.730034375</v>
+        <v>0.521909375</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>large</t>
+          <t>negligible</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -8048,28 +7984,28 @@
         <v>400</v>
       </c>
       <c r="F50" t="n">
-        <v>9.18</v>
+        <v>9.43</v>
       </c>
       <c r="G50" t="n">
         <v>4.91</v>
       </c>
       <c r="H50" t="n">
-        <v>3.779999999999999</v>
+        <v>3.7875</v>
       </c>
       <c r="I50" t="n">
-        <v>6381</v>
+        <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>4.780935321319239e-45</v>
+        <v>2.358504551631038e-64</v>
       </c>
       <c r="K50" t="n">
-        <v>1.110410784306404e-44</v>
+        <v>5.660410923914491e-64</v>
       </c>
       <c r="L50" t="b">
         <v>1</v>
       </c>
       <c r="M50" t="n">
-        <v>0.710940625</v>
+        <v>0.760303125</v>
       </c>
       <c r="N50" t="inlineStr">
         <is>
@@ -8108,28 +8044,28 @@
         <v>400</v>
       </c>
       <c r="F51" t="n">
-        <v>6.84</v>
+        <v>6.94</v>
       </c>
       <c r="G51" t="n">
         <v>4.91</v>
       </c>
       <c r="H51" t="n">
-        <v>1.395</v>
+        <v>1.420000000000001</v>
       </c>
       <c r="I51" t="n">
-        <v>12232</v>
+        <v>4790</v>
       </c>
       <c r="J51" t="n">
-        <v>3.911097176705411e-30</v>
+        <v>4.806020455855334e-49</v>
       </c>
       <c r="K51" t="n">
-        <v>7.61078369521053e-30</v>
+        <v>1.017745508298777e-48</v>
       </c>
       <c r="L51" t="b">
         <v>1</v>
       </c>
       <c r="M51" t="n">
-        <v>0.5660375</v>
+        <v>0.60566875</v>
       </c>
       <c r="N51" t="inlineStr">
         <is>
@@ -8168,32 +8104,32 @@
         <v>400</v>
       </c>
       <c r="F52" t="n">
-        <v>6.84</v>
+        <v>6.94</v>
       </c>
       <c r="G52" t="n">
         <v>4.91</v>
       </c>
       <c r="H52" t="n">
-        <v>1.39</v>
+        <v>1.405</v>
       </c>
       <c r="I52" t="n">
-        <v>16397.5</v>
+        <v>9704.5</v>
       </c>
       <c r="J52" t="n">
-        <v>2.112800801416368e-21</v>
+        <v>1.507075686974922e-35</v>
       </c>
       <c r="K52" t="n">
-        <v>3.710284334194598e-21</v>
+        <v>3.100269984634125e-35</v>
       </c>
       <c r="L52" t="b">
         <v>1</v>
       </c>
       <c r="M52" t="n">
-        <v>0.53355625</v>
+        <v>0.57093125</v>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>small</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -8228,37 +8164,37 @@
         <v>400</v>
       </c>
       <c r="F53" t="n">
-        <v>3.92</v>
+        <v>7.765000000000001</v>
       </c>
       <c r="G53" t="n">
         <v>4.91</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.21</v>
+        <v>2.6975</v>
       </c>
       <c r="I53" t="n">
-        <v>34800</v>
+        <v>18569.5</v>
       </c>
       <c r="J53" t="n">
-        <v>0.02198196673156593</v>
+        <v>1.332812757139437e-20</v>
       </c>
       <c r="K53" t="n">
-        <v>0.02552744523665721</v>
+        <v>2.460577397795884e-20</v>
       </c>
       <c r="L53" t="b">
         <v>1</v>
       </c>
       <c r="M53" t="n">
-        <v>0.471590625</v>
+        <v>0.69825625</v>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>ApproachA</t>
+          <t>ApproachB</t>
         </is>
       </c>
       <c r="P53" t="inlineStr"/>
@@ -8288,28 +8224,28 @@
         <v>400</v>
       </c>
       <c r="F54" t="n">
-        <v>3.55</v>
+        <v>5.779999999999999</v>
       </c>
       <c r="G54" t="n">
         <v>4.91</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.9175000000000002</v>
+        <v>1.395</v>
       </c>
       <c r="I54" t="n">
-        <v>23706.5</v>
+        <v>24545.5</v>
       </c>
       <c r="J54" t="n">
-        <v>1.38714509564957e-12</v>
+        <v>1.783747176353621e-11</v>
       </c>
       <c r="K54" t="n">
-        <v>2.322661555506257e-12</v>
+        <v>3.132434065791725e-11</v>
       </c>
       <c r="L54" t="b">
         <v>1</v>
       </c>
       <c r="M54" t="n">
-        <v>0.382571875</v>
+        <v>0.62699375</v>
       </c>
       <c r="N54" t="inlineStr">
         <is>
@@ -8318,7 +8254,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>ApproachA</t>
+          <t>ApproachB</t>
         </is>
       </c>
       <c r="P54" t="inlineStr"/>
@@ -8348,37 +8284,37 @@
         <v>400</v>
       </c>
       <c r="F55" t="n">
-        <v>2.71</v>
+        <v>4.225</v>
       </c>
       <c r="G55" t="n">
         <v>4.91</v>
       </c>
       <c r="H55" t="n">
-        <v>-1.65</v>
+        <v>-0.1549999999999998</v>
       </c>
       <c r="I55" t="n">
-        <v>8837</v>
+        <v>34847</v>
       </c>
       <c r="J55" t="n">
-        <v>1.32904170595827e-41</v>
+        <v>0.023185290731849</v>
       </c>
       <c r="K55" t="n">
-        <v>2.899727358454407e-41</v>
+        <v>0.0278223488782188</v>
       </c>
       <c r="L55" t="b">
         <v>1</v>
       </c>
       <c r="M55" t="n">
-        <v>0.285365625</v>
+        <v>0.5342625</v>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>large</t>
+          <t>negligible</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>ApproachA</t>
+          <t>ApproachB</t>
         </is>
       </c>
       <c r="P55" t="inlineStr"/>
@@ -8408,22 +8344,22 @@
         <v>400</v>
       </c>
       <c r="F56" t="n">
-        <v>2.005</v>
+        <v>13.61</v>
       </c>
       <c r="G56" t="n">
         <v>100</v>
       </c>
       <c r="H56" t="n">
-        <v>-97.995</v>
+        <v>-86.39</v>
       </c>
       <c r="I56" t="n">
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>2.412673020165349e-67</v>
+        <v>2.721964412235421e-67</v>
       </c>
       <c r="K56" t="n">
-        <v>1.130666132613922e-66</v>
+        <v>7.278391868362861e-67</v>
       </c>
       <c r="L56" t="b">
         <v>1</v>
@@ -8468,32 +8404,32 @@
         <v>400</v>
       </c>
       <c r="F57" t="n">
-        <v>2.4</v>
+        <v>14.35</v>
       </c>
       <c r="G57" t="n">
-        <v>7.56</v>
+        <v>100</v>
       </c>
       <c r="H57" t="n">
-        <v>-5.22</v>
+        <v>-85.65000000000001</v>
       </c>
       <c r="I57" t="n">
-        <v>9591</v>
+        <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>9.766407979267815e-40</v>
+        <v>2.726104985974824e-67</v>
       </c>
       <c r="K57" t="n">
-        <v>2.068180513256714e-39</v>
+        <v>7.278391868362861e-67</v>
       </c>
       <c r="L57" t="b">
         <v>1</v>
       </c>
       <c r="M57" t="n">
-        <v>0.345</v>
+        <v>0</v>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>large</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -8528,32 +8464,32 @@
         <v>400</v>
       </c>
       <c r="F58" t="n">
-        <v>2</v>
+        <v>13.79</v>
       </c>
       <c r="G58" t="n">
-        <v>2.53</v>
+        <v>100</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.7599999999999998</v>
+        <v>-86.21000000000001</v>
       </c>
       <c r="I58" t="n">
-        <v>20150</v>
+        <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>6.332733904399474e-18</v>
+        <v>2.725740519675975e-67</v>
       </c>
       <c r="K58" t="n">
-        <v>1.085611526468481e-17</v>
+        <v>7.278391868362861e-67</v>
       </c>
       <c r="L58" t="b">
         <v>1</v>
       </c>
       <c r="M58" t="n">
-        <v>0.3795875</v>
+        <v>0</v>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>large</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -8588,22 +8524,22 @@
         <v>400</v>
       </c>
       <c r="F59" t="n">
-        <v>2.005</v>
+        <v>13.61</v>
       </c>
       <c r="G59" t="n">
-        <v>0.205</v>
+        <v>1.7975</v>
       </c>
       <c r="H59" t="n">
-        <v>1.72</v>
+        <v>12.075</v>
       </c>
       <c r="I59" t="n">
         <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>2.669628368671761e-67</v>
+        <v>2.727947235340647e-67</v>
       </c>
       <c r="K59" t="n">
-        <v>1.130666132613922e-66</v>
+        <v>7.278391868362861e-67</v>
       </c>
       <c r="L59" t="b">
         <v>1</v>
@@ -8648,22 +8584,22 @@
         <v>400</v>
       </c>
       <c r="F60" t="n">
-        <v>2.4</v>
+        <v>14.35</v>
       </c>
       <c r="G60" t="n">
-        <v>0.205</v>
+        <v>1.7975</v>
       </c>
       <c r="H60" t="n">
-        <v>2.105</v>
+        <v>12.625</v>
       </c>
       <c r="I60" t="n">
         <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>2.661073006956787e-67</v>
+        <v>2.729224096990778e-67</v>
       </c>
       <c r="K60" t="n">
-        <v>1.130666132613922e-66</v>
+        <v>7.278391868362861e-67</v>
       </c>
       <c r="L60" t="b">
         <v>1</v>
@@ -8708,22 +8644,22 @@
         <v>400</v>
       </c>
       <c r="F61" t="n">
-        <v>2</v>
+        <v>13.79</v>
       </c>
       <c r="G61" t="n">
-        <v>0.205</v>
+        <v>1.7975</v>
       </c>
       <c r="H61" t="n">
-        <v>1.63</v>
+        <v>12.175</v>
       </c>
       <c r="I61" t="n">
         <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>2.666445086035864e-67</v>
+        <v>2.729396950636073e-67</v>
       </c>
       <c r="K61" t="n">
-        <v>1.130666132613922e-66</v>
+        <v>7.278391868362861e-67</v>
       </c>
       <c r="L61" t="b">
         <v>1</v>
@@ -8771,19 +8707,19 @@
         <v>100</v>
       </c>
       <c r="G62" t="n">
-        <v>0.205</v>
+        <v>1.7975</v>
       </c>
       <c r="H62" t="n">
-        <v>99.795</v>
+        <v>98.2025</v>
       </c>
       <c r="I62" t="n">
         <v>0</v>
       </c>
       <c r="J62" t="n">
-        <v>6.486318758726508e-68</v>
+        <v>2.64538389146274e-67</v>
       </c>
       <c r="K62" t="n">
-        <v>3.932440549228061e-67</v>
+        <v>7.278391868362861e-67</v>
       </c>
       <c r="L62" t="b">
         <v>1</v>
@@ -8828,22 +8764,22 @@
         <v>400</v>
       </c>
       <c r="F63" t="n">
-        <v>7.56</v>
+        <v>100</v>
       </c>
       <c r="G63" t="n">
-        <v>0.205</v>
+        <v>1.7975</v>
       </c>
       <c r="H63" t="n">
-        <v>7.255</v>
+        <v>98.2025</v>
       </c>
       <c r="I63" t="n">
         <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>7.100239880550665e-68</v>
+        <v>2.64538389146274e-67</v>
       </c>
       <c r="K63" t="n">
-        <v>3.932440549228061e-67</v>
+        <v>7.278391868362861e-67</v>
       </c>
       <c r="L63" t="b">
         <v>1</v>
@@ -8888,28 +8824,28 @@
         <v>400</v>
       </c>
       <c r="F64" t="n">
-        <v>2.53</v>
+        <v>100</v>
       </c>
       <c r="G64" t="n">
-        <v>0.205</v>
+        <v>1.7975</v>
       </c>
       <c r="H64" t="n">
-        <v>2.33</v>
+        <v>98.2025</v>
       </c>
       <c r="I64" t="n">
         <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>7.100239880550665e-68</v>
+        <v>2.64538389146274e-67</v>
       </c>
       <c r="K64" t="n">
-        <v>3.932440549228061e-67</v>
+        <v>7.278391868362861e-67</v>
       </c>
       <c r="L64" t="b">
         <v>1</v>
       </c>
       <c r="M64" t="n">
-        <v>0.99229375</v>
+        <v>1</v>
       </c>
       <c r="N64" t="inlineStr">
         <is>
@@ -8948,28 +8884,28 @@
         <v>416</v>
       </c>
       <c r="F65" t="n">
-        <v>5.57</v>
+        <v>9.81</v>
       </c>
       <c r="G65" t="n">
         <v>100</v>
       </c>
       <c r="H65" t="n">
-        <v>-92.45999999999999</v>
+        <v>-90.19</v>
       </c>
       <c r="I65" t="n">
-        <v>2925</v>
+        <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>2.609313895507326e-61</v>
+        <v>2.357874314768116e-71</v>
       </c>
       <c r="K65" t="n">
-        <v>8.218866312153356e-61</v>
+        <v>9.431497259072464e-71</v>
       </c>
       <c r="L65" t="b">
         <v>1</v>
       </c>
       <c r="M65" t="n">
-        <v>0.1769976192677515</v>
+        <v>0</v>
       </c>
       <c r="N65" t="inlineStr">
         <is>
@@ -9008,28 +8944,28 @@
         <v>416</v>
       </c>
       <c r="F66" t="n">
-        <v>3.65</v>
+        <v>7.55</v>
       </c>
       <c r="G66" t="n">
         <v>100</v>
       </c>
       <c r="H66" t="n">
-        <v>-94.19</v>
+        <v>-92.45</v>
       </c>
       <c r="I66" t="n">
-        <v>2926</v>
+        <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>2.625471183048989e-61</v>
+        <v>2.357874314768116e-71</v>
       </c>
       <c r="K66" t="n">
-        <v>8.218866312153356e-61</v>
+        <v>9.431497259072464e-71</v>
       </c>
       <c r="L66" t="b">
         <v>1</v>
       </c>
       <c r="M66" t="n">
-        <v>0.1774107803254438</v>
+        <v>0</v>
       </c>
       <c r="N66" t="inlineStr">
         <is>
@@ -9068,28 +9004,28 @@
         <v>416</v>
       </c>
       <c r="F67" t="n">
-        <v>3.21</v>
+        <v>7.55</v>
       </c>
       <c r="G67" t="n">
         <v>100</v>
       </c>
       <c r="H67" t="n">
-        <v>-94.19</v>
+        <v>-92.45</v>
       </c>
       <c r="I67" t="n">
-        <v>2926</v>
+        <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>2.616561147174345e-61</v>
+        <v>2.357874314768116e-71</v>
       </c>
       <c r="K67" t="n">
-        <v>8.218866312153356e-61</v>
+        <v>9.431497259072464e-71</v>
       </c>
       <c r="L67" t="b">
         <v>1</v>
       </c>
       <c r="M67" t="n">
-        <v>0.1790403106508876</v>
+        <v>0</v>
       </c>
       <c r="N67" t="inlineStr">
         <is>
@@ -9128,28 +9064,28 @@
         <v>416</v>
       </c>
       <c r="F68" t="n">
-        <v>5.57</v>
+        <v>9.81</v>
       </c>
       <c r="G68" t="n">
-        <v>2.7675</v>
+        <v>4.324999999999999</v>
       </c>
       <c r="H68" t="n">
-        <v>3.48</v>
+        <v>4.780000000000001</v>
       </c>
       <c r="I68" t="n">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>1.527014197472544e-69</v>
+        <v>2.357874314768116e-71</v>
       </c>
       <c r="K68" t="n">
-        <v>1.099450222180232e-68</v>
+        <v>9.431497259072464e-71</v>
       </c>
       <c r="L68" t="b">
         <v>1</v>
       </c>
       <c r="M68" t="n">
-        <v>0.9134615384615384</v>
+        <v>0.9852648853550295</v>
       </c>
       <c r="N68" t="inlineStr">
         <is>
@@ -9188,28 +9124,28 @@
         <v>416</v>
       </c>
       <c r="F69" t="n">
-        <v>3.65</v>
+        <v>7.55</v>
       </c>
       <c r="G69" t="n">
-        <v>2.7675</v>
+        <v>4.324999999999999</v>
       </c>
       <c r="H69" t="n">
-        <v>1.6075</v>
+        <v>2.52</v>
       </c>
       <c r="I69" t="n">
-        <v>4430.5</v>
+        <v>0</v>
       </c>
       <c r="J69" t="n">
-        <v>1.037936694942168e-56</v>
+        <v>2.357874314768116e-71</v>
       </c>
       <c r="K69" t="n">
-        <v>2.874286232147542e-56</v>
+        <v>9.431497259072464e-71</v>
       </c>
       <c r="L69" t="b">
         <v>1</v>
       </c>
       <c r="M69" t="n">
-        <v>0.776702339127219</v>
+        <v>0.7854047244822485</v>
       </c>
       <c r="N69" t="inlineStr">
         <is>
@@ -9248,28 +9184,28 @@
         <v>416</v>
       </c>
       <c r="F70" t="n">
-        <v>3.21</v>
+        <v>7.55</v>
       </c>
       <c r="G70" t="n">
-        <v>2.7675</v>
+        <v>4.324999999999999</v>
       </c>
       <c r="H70" t="n">
-        <v>1.185</v>
+        <v>2.52</v>
       </c>
       <c r="I70" t="n">
-        <v>5221</v>
+        <v>0</v>
       </c>
       <c r="J70" t="n">
-        <v>1.669870199611228e-54</v>
+        <v>2.357874314768116e-71</v>
       </c>
       <c r="K70" t="n">
-        <v>4.145884633517531e-54</v>
+        <v>9.431497259072464e-71</v>
       </c>
       <c r="L70" t="b">
         <v>1</v>
       </c>
       <c r="M70" t="n">
-        <v>0.7245198086168639</v>
+        <v>0.7460879715236687</v>
       </c>
       <c r="N70" t="inlineStr">
         <is>
@@ -9311,25 +9247,25 @@
         <v>100</v>
       </c>
       <c r="G71" t="n">
-        <v>2.7675</v>
+        <v>4.324999999999999</v>
       </c>
       <c r="H71" t="n">
-        <v>96.91500000000001</v>
+        <v>95.675</v>
       </c>
       <c r="I71" t="n">
-        <v>2800</v>
+        <v>0</v>
       </c>
       <c r="J71" t="n">
-        <v>2.10118130457541e-61</v>
+        <v>2.357874314768116e-71</v>
       </c>
       <c r="K71" t="n">
-        <v>7.564252696471475e-61</v>
+        <v>9.431497259072464e-71</v>
       </c>
       <c r="L71" t="b">
         <v>1</v>
       </c>
       <c r="M71" t="n">
-        <v>0.8505512666420119</v>
+        <v>1</v>
       </c>
       <c r="N71" t="inlineStr">
         <is>
@@ -9371,25 +9307,25 @@
         <v>100</v>
       </c>
       <c r="G72" t="n">
-        <v>2.7675</v>
+        <v>4.324999999999999</v>
       </c>
       <c r="H72" t="n">
-        <v>96.91500000000001</v>
+        <v>95.675</v>
       </c>
       <c r="I72" t="n">
-        <v>2926</v>
+        <v>0</v>
       </c>
       <c r="J72" t="n">
-        <v>4.91990072267415e-61</v>
+        <v>2.357874314768116e-71</v>
       </c>
       <c r="K72" t="n">
-        <v>1.416931408130155e-60</v>
+        <v>9.431497259072464e-71</v>
       </c>
       <c r="L72" t="b">
         <v>1</v>
       </c>
       <c r="M72" t="n">
-        <v>0.8267063840606509</v>
+        <v>1</v>
       </c>
       <c r="N72" t="inlineStr">
         <is>
@@ -9431,25 +9367,25 @@
         <v>100</v>
       </c>
       <c r="G73" t="n">
-        <v>2.7675</v>
+        <v>4.324999999999999</v>
       </c>
       <c r="H73" t="n">
-        <v>96.91500000000001</v>
+        <v>95.675</v>
       </c>
       <c r="I73" t="n">
-        <v>2926</v>
+        <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>4.919580436851137e-61</v>
+        <v>2.357874314768116e-71</v>
       </c>
       <c r="K73" t="n">
-        <v>1.416931408130155e-60</v>
+        <v>9.431497259072464e-71</v>
       </c>
       <c r="L73" t="b">
         <v>1</v>
       </c>
       <c r="M73" t="n">
-        <v>0.8216386603180473</v>
+        <v>1</v>
       </c>
       <c r="N73" t="inlineStr">
         <is>
